--- a/data/trans_orig/P57B2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido feliz en 2023</t>
+          <t>Población según se ha sentido feliz en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>157563</t>
+          <t>158540</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198293</t>
+          <t>198622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192627</t>
+          <t>190629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229940</t>
+          <t>230523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358943</t>
+          <t>361534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419465</t>
+          <t>416283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172415</t>
+          <t>172883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215096</t>
+          <t>212163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267467</t>
+          <t>268102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307136</t>
+          <t>310044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>453911</t>
+          <t>454779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511713</t>
+          <t>512577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93813</t>
+          <t>94253</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127762</t>
+          <t>127607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>192817</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231832</t>
+          <t>229855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>292354</t>
+          <t>293861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>347436</t>
+          <t>345371</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39903</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32319</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49873</t>
+          <t>49540</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56494</t>
+          <t>56088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>81352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1182296</t>
+          <t>1183568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1615352</t>
+          <t>1601566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>946987</t>
+          <t>932576</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1417365</t>
+          <t>1392438</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2179141</t>
+          <t>2170997</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2786779</t>
+          <t>2838395</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>490718</t>
+          <t>490411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>813613</t>
+          <t>812814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>625832</t>
+          <t>653128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>997306</t>
+          <t>1009816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1307127</t>
+          <t>1258329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1775257</t>
+          <t>1770724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>154360</t>
+          <t>152982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260273</t>
+          <t>260010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189049</t>
+          <t>187250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299745</t>
+          <t>302062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390118</t>
+          <t>371874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>541853</t>
+          <t>539653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56293</t>
+          <t>54647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32228</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>79304</t>
+          <t>78579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296610</t>
+          <t>296429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>355735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>286853</t>
+          <t>284099</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331585</t>
+          <t>330286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>600522</t>
+          <t>599293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>668252</t>
+          <t>670092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>228529</t>
+          <t>228102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>283742</t>
+          <t>282324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>251665</t>
+          <t>252912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>297312</t>
+          <t>297263</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>494974</t>
+          <t>493381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>562268</t>
+          <t>563266</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41059</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70158</t>
+          <t>71764</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51036</t>
+          <t>49955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78174</t>
+          <t>77878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101004</t>
+          <t>100108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139209</t>
+          <t>140101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33800</t>
+          <t>33780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1679062</t>
+          <t>1674624</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2199551</t>
+          <t>2181489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1453244</t>
+          <t>1462649</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2002341</t>
+          <t>1991751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3179309</t>
+          <t>3187671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3922083</t>
+          <t>3895169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>874617</t>
+          <t>901217</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1267089</t>
+          <t>1268943</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1170119</t>
+          <t>1171312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1566316</t>
+          <t>1553487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2259119</t>
+          <t>2258246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2779822</t>
+          <t>2779045</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>301539</t>
+          <t>299030</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>428621</t>
+          <t>431953</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>437210</t>
+          <t>436644</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>584013</t>
+          <t>584990</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>793726</t>
+          <t>793544</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>987374</t>
+          <t>990879</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93108</t>
+          <t>95887</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60210</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90831</t>
+          <t>91847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125566</t>
+          <t>125763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178815</t>
+          <t>177947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>178481</t>
+          <t>197355</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158540</t>
+          <t>173895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198622</t>
+          <t>219901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>210075</t>
+          <t>230861</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190629</t>
+          <t>210887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230523</t>
+          <t>251061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>388556</t>
+          <t>428217</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>361534</t>
+          <t>400749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>416283</t>
+          <t>460562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>193078</t>
+          <t>220703</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172883</t>
+          <t>198413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>212163</t>
+          <t>243032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>289138</t>
+          <t>319256</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268102</t>
+          <t>299115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310044</t>
+          <t>340899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>482216</t>
+          <t>539958</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454779</t>
+          <t>507845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512577</t>
+          <t>568961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109683</t>
+          <t>123492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94253</t>
+          <t>105973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127607</t>
+          <t>142356</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>209794</t>
+          <t>221607</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>190405</t>
+          <t>203384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>229855</t>
+          <t>242401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>319477</t>
+          <t>345098</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>293861</t>
+          <t>317385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>345371</t>
+          <t>369535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28448</t>
+          <t>31239</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>41836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39861</t>
+          <t>43293</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>34245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49540</t>
+          <t>53781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>68310</t>
+          <t>74532</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56088</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81352</t>
+          <t>89668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>509690</t>
+          <t>572788</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>509690</t>
+          <t>572788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509690</t>
+          <t>572788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>748869</t>
+          <t>815017</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>748869</t>
+          <t>815017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>748869</t>
+          <t>815017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1258559</t>
+          <t>1387805</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1258559</t>
+          <t>1387805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1258559</t>
+          <t>1387805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1320957</t>
+          <t>1162310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1183568</t>
+          <t>1109876</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1601566</t>
+          <t>1215174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1090624</t>
+          <t>996936</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>932576</t>
+          <t>956569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1392438</t>
+          <t>1044471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2411581</t>
+          <t>2159246</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2170997</t>
+          <t>2084523</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2838395</t>
+          <t>2225319</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>707954</t>
+          <t>780188</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>490411</t>
+          <t>727153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>812814</t>
+          <t>829254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>863186</t>
+          <t>851947</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>653128</t>
+          <t>807012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1009816</t>
+          <t>891598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1571140</t>
+          <t>1632135</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1258329</t>
+          <t>1564132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1770724</t>
+          <t>1701570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>218505</t>
+          <t>242938</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152982</t>
+          <t>213919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>260010</t>
+          <t>274429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>258533</t>
+          <t>294332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187250</t>
+          <t>267451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302062</t>
+          <t>323192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>477038</t>
+          <t>537270</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371874</t>
+          <t>499393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>539653</t>
+          <t>579389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36837</t>
+          <t>38244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54647</t>
+          <t>54539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>34772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>59278</t>
+          <t>63231</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>49670</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78579</t>
+          <t>80908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2284252</t>
+          <t>2223679</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2284252</t>
+          <t>2223679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2284252</t>
+          <t>2223679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2234785</t>
+          <t>2168203</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2234785</t>
+          <t>2168203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2234785</t>
+          <t>2168203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4519037</t>
+          <t>4391882</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4519037</t>
+          <t>4391882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4519037</t>
+          <t>4391882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>326270</t>
+          <t>358998</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296429</t>
+          <t>331447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355735</t>
+          <t>387838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>308491</t>
+          <t>345767</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284099</t>
+          <t>322105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330286</t>
+          <t>369288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>634761</t>
+          <t>704764</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>599293</t>
+          <t>662185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>670092</t>
+          <t>740008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254248</t>
+          <t>282631</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>228102</t>
+          <t>252570</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>282324</t>
+          <t>311567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>274461</t>
+          <t>299730</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>252912</t>
+          <t>275835</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>297263</t>
+          <t>322255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>528709</t>
+          <t>582361</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>493381</t>
+          <t>547425</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>563266</t>
+          <t>626648</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>55293</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>45492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71764</t>
+          <t>75464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63184</t>
+          <t>73750</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49955</t>
+          <t>59872</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77878</t>
+          <t>90865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>118477</t>
+          <t>132445</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100108</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>154851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22733</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>644235</t>
+          <t>709003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644235</t>
+          <t>709003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644235</t>
+          <t>709003</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660302</t>
+          <t>734172</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660302</t>
+          <t>734172</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660302</t>
+          <t>734172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1304537</t>
+          <t>1443175</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1304537</t>
+          <t>1443175</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1304537</t>
+          <t>1443175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1825708</t>
+          <t>1718663</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1674624</t>
+          <t>1651796</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2181489</t>
+          <t>1786807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1609190</t>
+          <t>1573564</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1462649</t>
+          <t>1524075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1991751</t>
+          <t>1627937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3434897</t>
+          <t>3292227</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3187671</t>
+          <t>3199387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3895169</t>
+          <t>3371140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1155280</t>
+          <t>1283522</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>901217</t>
+          <t>1226571</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1268943</t>
+          <t>1347222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1426784</t>
+          <t>1470932</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1171312</t>
+          <t>1426126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1553487</t>
+          <t>1525372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2582065</t>
+          <t>2754454</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2258246</t>
+          <t>2675677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2779045</t>
+          <t>2843028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>383480</t>
+          <t>425124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>299030</t>
+          <t>387675</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>431953</t>
+          <t>462829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>531511</t>
+          <t>589689</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>436644</t>
+          <t>554686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>584990</t>
+          <t>626218</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>914991</t>
+          <t>1014813</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>793544</t>
+          <t>967029</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>990879</t>
+          <t>1072545</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>73709</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>61018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95887</t>
+          <t>98898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>76470</t>
+          <t>83206</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60591</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91847</t>
+          <t>97151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>150178</t>
+          <t>161367</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>125763</t>
+          <t>139164</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177947</t>
+          <t>186037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3438177</t>
+          <t>3505470</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3438177</t>
+          <t>3505470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3438177</t>
+          <t>3505470</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3643955</t>
+          <t>3717391</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3643955</t>
+          <t>3717391</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3643955</t>
+          <t>3717391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7082132</t>
+          <t>7222861</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7082132</t>
+          <t>7222861</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7082132</t>
+          <t>7222861</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
